--- a/DesignerConfigs/Datas/PayChannel.xlsx
+++ b/DesignerConfigs/Datas/PayChannel.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -111,136 +111,127 @@
     <t>PayPal</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/paypal.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/paypal_s.png</t>
+    <t>UI/PayType/TogglePic/paypal.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/paypal_s.png</t>
   </si>
   <si>
     <t>Venmo</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/venmo.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/venmo_s.png</t>
+    <t>UI/PayType/TogglePic/venmo.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/venmo_s.png</t>
   </si>
   <si>
     <t>zelle</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/zelle.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/zelle_s.png</t>
+    <t>UI/PayType/TogglePic/zelle.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/zelle_s.png</t>
   </si>
   <si>
     <t>Interac e-Transfer</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/etransfer.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/etransfer_s.png</t>
+    <t>UI/PayType/TogglePic/etransfer.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/etransfer_s.png</t>
   </si>
   <si>
     <t>Mercado Pago</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/pago.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/pago_s.png</t>
+    <t>UI/PayType/TogglePic/pago.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/pago_s.png</t>
   </si>
   <si>
     <t>BBVA Wallet</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/bbva.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/bbva_s.png</t>
+    <t>UI/PayType/TogglePic/bbva.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/bbva_s.png</t>
   </si>
   <si>
     <t>Pix</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/pix.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/pix_s.png</t>
+    <t>UI/PayType/TogglePic/pix.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/pix_s.png</t>
   </si>
   <si>
     <t>PicPay</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/picpay.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/picpay_s.png</t>
+    <t>UI/PayType/TogglePic/picpay.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/picpay_s.png</t>
   </si>
   <si>
     <t>Skrill</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/skrill.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/skrill_s.png</t>
+    <t>UI/PayType/TogglePic/skrill.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/skrill_s.png</t>
   </si>
   <si>
     <t>Revolut</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/revolut.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/revolut_s.png</t>
+    <t>UI/PayType/TogglePic/revolut.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/revolut_s.png</t>
   </si>
   <si>
     <t>Sofort Banking</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/sofort.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/sofort_s.png</t>
+    <t>UI/PayType/TogglePic/sofort.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/sofort_s.png</t>
   </si>
   <si>
     <t>Paylib</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/paylib.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/paylib_s.png</t>
+    <t>UI/PayType/TogglePic/paylib.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/paylib_s.png</t>
   </si>
   <si>
     <t>PayPay</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/paypay.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/paypay_s.png</t>
-  </si>
-  <si>
-    <t>CashApp</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/TogglePic/cashapp.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/cashapp_s.png</t>
+    <t>UI/PayType/TogglePic/paypay.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/paypay_s.png</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/other.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/other_s.png</t>
+    <t>UI/PayType/TogglePic/other.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/other_s.png</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="17.6666666666667" customWidth="1"/>
@@ -1533,30 +1524,13 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
         <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/PayChannel.xlsx
+++ b/DesignerConfigs/Datas/PayChannel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -225,13 +225,22 @@
     <t>UI/PayType/Icon/paypay_s.png</t>
   </si>
   <si>
+    <t>CashApp</t>
+  </si>
+  <si>
+    <t>Sprites/UI/PayType/TogglePic/cashapp.png</t>
+  </si>
+  <si>
+    <t>Sprites/UI/PayType/Icon/cashapp_s.png</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>UI/PayType/TogglePic/other.png</t>
-  </si>
-  <si>
-    <t>UI/PayType/Icon/other_s.png</t>
+    <t>Sprites/UI/PayType/TogglePic/other.png</t>
+  </si>
+  <si>
+    <t>Sprites/UI/PayType/Icon/other_s.png</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="17.6666666666667" customWidth="1"/>
@@ -1524,13 +1533,30 @@
         <v>54</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
         <v>55</v>
       </c>
       <c r="F19" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/PayChannel.xlsx
+++ b/DesignerConfigs/Datas/PayChannel.xlsx
@@ -1414,7 +1414,7 @@
         <v>33</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>34</v>

--- a/DesignerConfigs/Datas/PayChannel.xlsx
+++ b/DesignerConfigs/Datas/PayChannel.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\_Project\AsWaterGameProj\DesignerConfigs\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -228,19 +233,19 @@
     <t>CashApp</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/cashapp.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/cashapp_s.png</t>
+    <t>UI/PayType/TogglePic/cashapp.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/cashapp_s.png</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>Sprites/UI/PayType/TogglePic/other.png</t>
-  </si>
-  <si>
-    <t>Sprites/UI/PayType/Icon/other_s.png</t>
+    <t>UI/PayType/TogglePic/other.png</t>
+  </si>
+  <si>
+    <t>UI/PayType/Icon/Icon/other_s.png</t>
   </si>
 </sst>
 </file>
